--- a/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_persona_zeroshot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_clap_gpt-4o_persona_zeroshot.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10574,7 +10574,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11305,7 +11305,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11407,7 +11407,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11968,7 +11968,7 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -12053,7 +12053,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12682,7 +12682,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -13668,7 +13668,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16762,7 +16762,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -16813,7 +16813,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16847,7 +16847,7 @@
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -17969,7 +17969,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18547,7 +18547,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18632,7 +18632,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18700,7 +18700,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18751,7 +18751,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18802,7 +18802,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18870,7 +18870,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -19006,7 +19006,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19040,7 +19040,7 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19091,7 +19091,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19125,7 +19125,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19516,7 @@
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -19805,7 +19805,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19839,7 +19839,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -19890,7 +19890,7 @@
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20162,7 +20162,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20213,7 +20213,7 @@
       </c>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20417,7 +20417,7 @@
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20519,7 +20519,7 @@
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20536,7 +20536,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20876,7 +20876,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20893,7 +20893,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -21148,7 +21148,7 @@
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -21233,7 +21233,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21318,7 +21318,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21335,7 +21335,7 @@
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21505,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21641,7 +21641,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21692,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21726,7 +21726,7 @@
       </c>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -21743,7 +21743,7 @@
       </c>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21794,7 +21794,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21811,7 +21811,7 @@
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21913,7 +21913,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -21964,7 +21964,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21981,7 +21981,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21998,7 +21998,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22032,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22100,7 +22100,7 @@
       </c>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22168,7 +22168,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22202,7 +22202,7 @@
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22287,7 +22287,7 @@
       </c>
       <c r="C1286" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22304,7 +22304,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22321,7 +22321,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22372,7 +22372,7 @@
       </c>
       <c r="C1291" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22440,7 +22440,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22593,7 +22593,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22661,7 +22661,7 @@
       </c>
       <c r="C1308" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22763,7 +22763,7 @@
       </c>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C1317" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22848,7 +22848,7 @@
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C1325" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22984,7 +22984,7 @@
       </c>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23086,7 +23086,7 @@
       </c>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23120,7 +23120,7 @@
       </c>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23137,7 +23137,7 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23154,7 +23154,7 @@
       </c>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23239,7 +23239,7 @@
       </c>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23358,7 +23358,7 @@
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23375,7 +23375,7 @@
       </c>
       <c r="C1350" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23392,7 +23392,7 @@
       </c>
       <c r="C1351" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -23426,7 +23426,7 @@
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23460,7 +23460,7 @@
       </c>
       <c r="C1355" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23528,7 +23528,7 @@
       </c>
       <c r="C1359" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="C1360" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23613,7 +23613,7 @@
       </c>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="C1367" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23681,7 +23681,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23970,7 +23970,7 @@
       </c>
       <c r="C1385" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23987,7 +23987,7 @@
       </c>
       <c r="C1386" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24004,7 +24004,7 @@
       </c>
       <c r="C1387" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24055,7 +24055,7 @@
       </c>
       <c r="C1390" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24072,7 +24072,7 @@
       </c>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24106,7 +24106,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24123,7 +24123,7 @@
       </c>
       <c r="C1394" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24157,7 +24157,7 @@
       </c>
       <c r="C1396" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24412,7 +24412,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24480,7 @@
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24582,7 +24582,7 @@
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -24650,7 +24650,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24735,7 +24735,7 @@
       </c>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24752,7 +24752,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24888,7 +24888,7 @@
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24905,7 +24905,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24922,7 +24922,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -25007,7 +25007,7 @@
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25092,7 +25092,7 @@
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25126,7 +25126,7 @@
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25160,7 +25160,7 @@
       </c>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25245,7 +25245,7 @@
       </c>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25364,7 +25364,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25415,7 +25415,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25432,7 +25432,7 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25602,7 +25602,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -25840,7 +25840,7 @@
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -25857,7 +25857,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25874,7 +25874,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -25908,7 +25908,7 @@
       </c>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -25925,7 +25925,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="C1502" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25976,7 +25976,7 @@
       </c>
       <c r="C1503" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26095,7 +26095,7 @@
       </c>
       <c r="C1510" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26180,7 +26180,7 @@
       </c>
       <c r="C1515" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -26333,7 +26333,7 @@
       </c>
       <c r="C1524" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26350,7 +26350,7 @@
       </c>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -26503,7 +26503,7 @@
       </c>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -27098,7 +27098,7 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -27217,7 +27217,7 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -27285,7 +27285,7 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -27506,7 +27506,7 @@
       </c>
       <c r="C1593" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27727,7 +27727,7 @@
       </c>
       <c r="C1606" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -28271,7 +28271,7 @@
       </c>
       <c r="C1638" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28322,7 +28322,7 @@
       </c>
       <c r="C1641" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28390,7 +28390,7 @@
       </c>
       <c r="C1645" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28509,7 +28509,7 @@
       </c>
       <c r="C1652" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -28866,7 +28866,7 @@
       </c>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -28951,7 +28951,7 @@
       </c>
       <c r="C1678" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29155,7 +29155,7 @@
       </c>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="C1693" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29240,7 +29240,7 @@
       </c>
       <c r="C1695" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29478,7 +29478,7 @@
       </c>
       <c r="C1709" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29597,7 +29597,7 @@
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -29614,7 +29614,7 @@
       </c>
       <c r="C1717" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29682,7 +29682,7 @@
       </c>
       <c r="C1721" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -29835,7 +29835,7 @@
       </c>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -29886,7 +29886,7 @@
       </c>
       <c r="C1733" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -29903,7 +29903,7 @@
       </c>
       <c r="C1734" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29920,7 @@
       </c>
       <c r="C1735" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="C1736" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="C1737" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -30158,7 +30158,7 @@
       </c>
       <c r="C1749" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30379,7 +30379,7 @@
       </c>
       <c r="C1762" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="C1772" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30787,7 +30787,7 @@
       </c>
       <c r="C1786" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -30804,7 +30804,7 @@
       </c>
       <c r="C1787" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -30821,7 +30821,7 @@
       </c>
       <c r="C1788" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30872,7 +30872,7 @@
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30940,7 +30940,7 @@
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="C1799" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -31025,7 +31025,7 @@
       </c>
       <c r="C1800" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -31076,7 +31076,7 @@
       </c>
       <c r="C1803" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="C1821" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31705,7 +31705,7 @@
       </c>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31739,7 +31739,7 @@
       </c>
       <c r="C1842" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -32045,7 +32045,7 @@
       </c>
       <c r="C1860" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -32147,7 +32147,7 @@
       </c>
       <c r="C1866" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="C1867" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C1885" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="C1894" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32640,7 +32640,7 @@
       </c>
       <c r="C1895" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="C1910" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33167,7 +33167,7 @@
       </c>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33201,7 +33201,7 @@
       </c>
       <c r="C1928" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="C1930" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="C1935" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33694,7 +33694,7 @@
       </c>
       <c r="C1957" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33779,7 +33779,7 @@
       </c>
       <c r="C1962" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="C1965" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33847,7 +33847,7 @@
       </c>
       <c r="C1966" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33898,7 +33898,7 @@
       </c>
       <c r="C1969" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33932,7 +33932,7 @@
       </c>
       <c r="C1971" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="C1973" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
       </c>
       <c r="C1992" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="C1995" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34374,7 +34374,7 @@
       </c>
       <c r="C1997" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34459,7 +34459,7 @@
       </c>
       <c r="C2002" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34629,7 +34629,7 @@
       </c>
       <c r="C2012" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="C2026" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34918,7 +34918,7 @@
       </c>
       <c r="C2029" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35020,7 +35020,7 @@
       </c>
       <c r="C2035" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35105,7 +35105,7 @@
       </c>
       <c r="C2040" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="C2061" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35615,7 +35615,7 @@
       </c>
       <c r="C2070" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35717,7 +35717,7 @@
       </c>
       <c r="C2076" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="C2095" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36193,7 +36193,7 @@
       </c>
       <c r="C2104" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36244,7 +36244,7 @@
       </c>
       <c r="C2107" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="C2119" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36482,7 +36482,7 @@
       </c>
       <c r="C2121" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36499,7 +36499,7 @@
       </c>
       <c r="C2122" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36839,7 +36839,7 @@
       </c>
       <c r="C2142" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37043,7 +37043,7 @@
       </c>
       <c r="C2154" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37111,7 +37111,7 @@
       </c>
       <c r="C2158" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37145,7 +37145,7 @@
       </c>
       <c r="C2160" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37213,7 +37213,7 @@
       </c>
       <c r="C2164" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -37502,7 +37502,7 @@
       </c>
       <c r="C2181" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C2196" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37859,7 +37859,7 @@
       </c>
       <c r="C2202" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37876,7 +37876,7 @@
       </c>
       <c r="C2203" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38063,7 +38063,7 @@
       </c>
       <c r="C2214" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38114,7 +38114,7 @@
       </c>
       <c r="C2217" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38131,7 +38131,7 @@
       </c>
       <c r="C2218" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38165,7 +38165,7 @@
       </c>
       <c r="C2220" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38233,7 +38233,7 @@
       </c>
       <c r="C2224" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -38284,7 +38284,7 @@
       </c>
       <c r="C2227" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38318,7 +38318,7 @@
       </c>
       <c r="C2229" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38335,7 +38335,7 @@
       </c>
       <c r="C2230" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38352,7 +38352,7 @@
       </c>
       <c r="C2231" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38488,7 +38488,7 @@
       </c>
       <c r="C2239" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38777,7 +38777,7 @@
       </c>
       <c r="C2256" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
       </c>
       <c r="C2264" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -38947,7 +38947,7 @@
       </c>
       <c r="C2266" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39049,7 +39049,7 @@
       </c>
       <c r="C2272" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39117,7 +39117,7 @@
       </c>
       <c r="C2276" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39134,7 +39134,7 @@
       </c>
       <c r="C2277" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39440,7 +39440,7 @@
       </c>
       <c r="C2295" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39491,7 +39491,7 @@
       </c>
       <c r="C2298" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39593,7 +39593,7 @@
       </c>
       <c r="C2304" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39610,7 +39610,7 @@
       </c>
       <c r="C2305" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39661,7 +39661,7 @@
       </c>
       <c r="C2308" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39746,7 +39746,7 @@
       </c>
       <c r="C2313" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40120,7 +40120,7 @@
       </c>
       <c r="C2335" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40188,7 +40188,7 @@
       </c>
       <c r="C2339" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40222,7 +40222,7 @@
       </c>
       <c r="C2341" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40239,7 +40239,7 @@
       </c>
       <c r="C2342" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40341,7 +40341,7 @@
       </c>
       <c r="C2348" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40511,7 +40511,7 @@
       </c>
       <c r="C2358" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40562,7 +40562,7 @@
       </c>
       <c r="C2361" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40579,7 +40579,7 @@
       </c>
       <c r="C2362" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40783,7 +40783,7 @@
       </c>
       <c r="C2374" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40817,7 +40817,7 @@
       </c>
       <c r="C2376" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40851,7 +40851,7 @@
       </c>
       <c r="C2378" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -40987,7 +40987,7 @@
       </c>
       <c r="C2386" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="C2394" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41140,7 +41140,7 @@
       </c>
       <c r="C2395" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41174,7 +41174,7 @@
       </c>
       <c r="C2397" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41208,7 +41208,7 @@
       </c>
       <c r="C2399" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41531,7 +41531,7 @@
       </c>
       <c r="C2418" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41582,7 +41582,7 @@
       </c>
       <c r="C2421" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41633,7 +41633,7 @@
       </c>
       <c r="C2424" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41684,7 +41684,7 @@
       </c>
       <c r="C2427" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41735,7 +41735,7 @@
       </c>
       <c r="C2430" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41769,7 +41769,7 @@
       </c>
       <c r="C2432" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42347,7 +42347,7 @@
       </c>
       <c r="C2466" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42500,7 +42500,7 @@
       </c>
       <c r="C2475" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="C2481" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -43129,7 +43129,7 @@
       </c>
       <c r="C2512" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -43282,7 +43282,7 @@
       </c>
       <c r="C2521" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43333,7 +43333,7 @@
       </c>
       <c r="C2524" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43384,7 +43384,7 @@
       </c>
       <c r="C2527" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43418,7 +43418,7 @@
       </c>
       <c r="C2529" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43469,7 +43469,7 @@
       </c>
       <c r="C2532" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="C2538" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43622,7 +43622,7 @@
       </c>
       <c r="C2541" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43877,7 +43877,7 @@
       </c>
       <c r="C2556" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -44336,7 +44336,7 @@
       </c>
       <c r="C2583" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44540,7 +44540,7 @@
       </c>
       <c r="C2595" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44778,7 +44778,7 @@
       </c>
       <c r="C2609" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44965,7 +44965,7 @@
       </c>
       <c r="C2620" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45050,7 +45050,7 @@
       </c>
       <c r="C2625" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45067,7 +45067,7 @@
       </c>
       <c r="C2626" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45101,7 +45101,7 @@
       </c>
       <c r="C2628" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -45390,7 +45390,7 @@
       </c>
       <c r="C2645" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45679,7 +45679,7 @@
       </c>
       <c r="C2662" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45713,7 +45713,7 @@
       </c>
       <c r="C2664" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46240,7 +46240,7 @@
       </c>
       <c r="C2695" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46427,7 +46427,7 @@
       </c>
       <c r="C2706" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46512,7 +46512,7 @@
       </c>
       <c r="C2711" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46682,7 +46682,7 @@
       </c>
       <c r="C2721" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46784,7 +46784,7 @@
       </c>
       <c r="C2727" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46818,7 +46818,7 @@
       </c>
       <c r="C2729" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -47090,7 +47090,7 @@
       </c>
       <c r="C2745" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47209,7 +47209,7 @@
       </c>
       <c r="C2752" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47345,7 +47345,7 @@
       </c>
       <c r="C2760" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47362,7 +47362,7 @@
       </c>
       <c r="C2761" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47430,7 +47430,7 @@
       </c>
       <c r="C2765" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -47515,7 +47515,7 @@
       </c>
       <c r="C2770" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47549,7 +47549,7 @@
       </c>
       <c r="C2772" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -47685,7 +47685,7 @@
       </c>
       <c r="C2780" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="C2794" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48161,7 +48161,7 @@
       </c>
       <c r="C2808" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48212,7 +48212,7 @@
       </c>
       <c r="C2811" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48331,7 +48331,7 @@
       </c>
       <c r="C2818" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48518,7 +48518,7 @@
       </c>
       <c r="C2829" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -48552,7 +48552,7 @@
       </c>
       <c r="C2831" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48875,7 +48875,7 @@
       </c>
       <c r="C2850" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -48977,7 +48977,7 @@
       </c>
       <c r="C2856" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49045,7 +49045,7 @@
       </c>
       <c r="C2860" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49130,7 +49130,7 @@
       </c>
       <c r="C2865" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49249,7 +49249,7 @@
       </c>
       <c r="C2872" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -49283,7 +49283,7 @@
       </c>
       <c r="C2874" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
       </c>
       <c r="C2879" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -49912,7 +49912,7 @@
       </c>
       <c r="C2911" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -50048,7 +50048,7 @@
       </c>
       <c r="C2919" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50116,7 +50116,7 @@
       </c>
       <c r="C2923" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50133,7 +50133,7 @@
       </c>
       <c r="C2924" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50252,7 +50252,7 @@
       </c>
       <c r="C2931" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50286,7 +50286,7 @@
       </c>
       <c r="C2933" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -50405,7 +50405,7 @@
       </c>
       <c r="C2940" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50915,7 +50915,7 @@
       </c>
       <c r="C2970" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50966,7 +50966,7 @@
       </c>
       <c r="C2973" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -51170,7 +51170,7 @@
       </c>
       <c r="C2985" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -51187,7 +51187,7 @@
       </c>
       <c r="C2986" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -51238,7 +51238,7 @@
       </c>
       <c r="C2989" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -51479,7 +51479,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.544</v>
+        <v>0.5136666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -51489,7 +51489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5757822527727197</v>
+        <v>0.5757044192866464</v>
       </c>
     </row>
     <row r="4">
@@ -51499,7 +51499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5804507587568966</v>
+        <v>0.526559187887625</v>
       </c>
     </row>
     <row r="5">
@@ -51509,7 +51509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5948097963775144</v>
+        <v>0.6124500367625428</v>
       </c>
     </row>
     <row r="6">
@@ -51519,7 +51519,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7098623253565107</v>
+        <v>0.7145508481587601</v>
       </c>
     </row>
     <row r="7">
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>685.6396612319995</v>
+        <v>1712.489032857004</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2285465537439998</v>
+        <v>0.5708296776190012</v>
       </c>
     </row>
   </sheetData>
